--- a/docs/DemoFX_設計書.xlsx
+++ b/docs/DemoFX_設計書.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{F943977D-173D-423C-A073-7C4837641D95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="00_概要" sheetId="1" r:id="rId1"/>
@@ -1814,12 +1814,12 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -2261,18 +2261,18 @@
       </c>
     </row>
     <row r="2" spans="1:3" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="11" t="s">
         <v>409</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="9" t="s">
         <v>410</v>
       </c>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A4" s="8" t="s">
@@ -2363,11 +2363,11 @@
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="9" t="s">
         <v>433</v>
       </c>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A13" s="8" t="s">
@@ -2435,11 +2435,11 @@
       <c r="C19" s="6"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="9" t="s">
         <v>442</v>
       </c>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="10"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A21" s="8" t="s">
@@ -2491,11 +2491,11 @@
       <c r="C25" s="6"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A26" s="11" t="s">
+      <c r="A26" s="9" t="s">
         <v>450</v>
       </c>
-      <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="10"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A27" s="8" t="s">
@@ -2560,11 +2560,11 @@
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A33" s="11" t="s">
+      <c r="A33" s="9" t="s">
         <v>461</v>
       </c>
-      <c r="B33" s="12"/>
-      <c r="C33" s="12"/>
+      <c r="B33" s="10"/>
+      <c r="C33" s="10"/>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A34" s="8" t="s">
@@ -2625,11 +2625,11 @@
       <c r="C39" s="6"/>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A40" s="11" t="s">
+      <c r="A40" s="9" t="s">
         <v>470</v>
       </c>
-      <c r="B40" s="12"/>
-      <c r="C40" s="12"/>
+      <c r="B40" s="10"/>
+      <c r="C40" s="10"/>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A41" s="8" t="s">
@@ -2670,11 +2670,11 @@
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A45" s="11" t="s">
+      <c r="A45" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="B45" s="12"/>
-      <c r="C45" s="12"/>
+      <c r="B45" s="10"/>
+      <c r="C45" s="10"/>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A46" s="8" t="s">
@@ -2715,11 +2715,11 @@
       <c r="C49" s="6"/>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A50" s="11" t="s">
+      <c r="A50" s="9" t="s">
         <v>480</v>
       </c>
-      <c r="B50" s="12"/>
-      <c r="C50" s="12"/>
+      <c r="B50" s="10"/>
+      <c r="C50" s="10"/>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A51" s="8" t="s">
@@ -2780,11 +2780,11 @@
       <c r="C56" s="6"/>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A57" s="11" t="s">
+      <c r="A57" s="9" t="s">
         <v>488</v>
       </c>
-      <c r="B57" s="12"/>
-      <c r="C57" s="12"/>
+      <c r="B57" s="10"/>
+      <c r="C57" s="10"/>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A58" s="8" t="s">
@@ -2839,6 +2839,8 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A57:C57"/>
+    <mergeCell ref="A40:C40"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A20:C20"/>
@@ -2847,8 +2849,6 @@
     <mergeCell ref="A33:C33"/>
     <mergeCell ref="A26:C26"/>
     <mergeCell ref="A45:C45"/>
-    <mergeCell ref="A57:C57"/>
-    <mergeCell ref="A40:C40"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3760,13 +3760,13 @@
       </c>
     </row>
     <row r="15" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A15" s="9" t="s">
+      <c r="A15" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="1">
